--- a/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
+++ b/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
@@ -13,8 +13,20 @@
     <sheet name="대체품" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$H$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'대체품'!$A$6:$H$7</definedName>
+    <definedName name="reply_containment_scope">'대책서'!$B$25</definedName>
+    <definedName name="reply_containment">'대책서'!$B$26</definedName>
+    <definedName name="reply_root_cause">'대책서'!$B$29</definedName>
+    <definedName name="reply_escape_cause">'대책서'!$B$32</definedName>
+    <definedName name="reply_prevention">'대책서'!$B$35</definedName>
+    <definedName name="reply_verify_period">'대책서'!$B$39</definedName>
+    <definedName name="reply_verify_recipe">'대책서'!$D$39</definedName>
+    <definedName name="reply_verify_inspected">'대책서'!$E$39</definedName>
+    <definedName name="reply_verify_defective">'대책서'!$F$39</definedName>
+    <definedName name="reply_verify_status">'대책서'!$H$39</definedName>
+    <definedName name="reply_verify_note">'대책서'!$B$40</definedName>
+    <definedName name="reply_closed_at">'대책서'!$F$41</definedName>
+    <definedName name="reply_closure_note">'대책서'!$B$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$H$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,10 +34,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="+0.00&quot;%p&quot;;-0.00&quot;%p&quot;"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;배&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot; PPM&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,27 +50,24 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <sz val="20"/>
+      <color rgb="00262626"/>
+      <sz val="17"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
+      <color rgb="00262626"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
+      <color rgb="00262626"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="00262626"/>
       <sz val="9"/>
     </font>
     <font>
@@ -67,50 +78,74 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00000000"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00262626"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="009C2A2A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00262626"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00262626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00262626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F3864"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="00808080"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00262626"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00808080"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00808080"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00808080"/>
-      <sz val="7.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -124,7 +159,7 @@
       <sz val="7.5"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -134,6 +169,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,11 +188,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDE6F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF3FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBF0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DCE3EF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -174,10 +229,29 @@
         <color rgb="00A6A6A6"/>
       </bottom>
     </border>
+    <border/>
     <border>
-      <left style="medium">
-        <color rgb="00595959"/>
-      </left>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="00A6A6A6"/>
       </right>
@@ -187,110 +261,24 @@
       <bottom style="thin">
         <color rgb="00A6A6A6"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00A6A6A6"/>
-      </left>
-      <right style="medium">
-        <color rgb="00595959"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="00A6A6A6"/>
       </top>
       <bottom style="thin">
         <color rgb="00A6A6A6"/>
       </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00595959"/>
-      </left>
-      <right style="thin">
-        <color rgb="00A6A6A6"/>
-      </right>
-      <top style="medium">
-        <color rgb="00595959"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00A6A6A6"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00595959"/>
-      </left>
-      <right style="thin">
-        <color rgb="00A6A6A6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00A6A6A6"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00595959"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00A6A6A6"/>
-      </left>
-      <right style="thin">
-        <color rgb="00A6A6A6"/>
-      </right>
-      <top style="medium">
-        <color rgb="00595959"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00A6A6A6"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00A6A6A6"/>
-      </left>
-      <right style="thin">
-        <color rgb="00A6A6A6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00A6A6A6"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00595959"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00A6A6A6"/>
-      </left>
-      <right style="medium">
-        <color rgb="00595959"/>
-      </right>
-      <top style="medium">
-        <color rgb="00595959"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00A6A6A6"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00A6A6A6"/>
-      </left>
-      <right style="medium">
-        <color rgb="00595959"/>
-      </right>
-      <top style="thin">
-        <color rgb="00A6A6A6"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00595959"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -301,132 +289,131 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -793,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -835,18 +822,12 @@
       </c>
     </row>
     <row r="2" ht="17" customHeight="1">
-      <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
     </row>
-    <row r="3" ht="17" customHeight="1">
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="7" customHeight="1"/>
+    <row r="3" ht="17" customHeight="1"/>
+    <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -858,9 +839,7 @@
           <t>{{alert_code}}</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>발행일시</t>
         </is>
@@ -870,664 +849,632 @@
           <t>{{issued_at}}</t>
         </is>
       </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="9" t="n"/>
-    </row>
-    <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>담당자</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>대상 부품</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>{{part_id}} · {{part_name}} ({{group_id}} / {{category_label}})</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>불량 유형</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>{{defect_type}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>주관 담당</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>{{assignee}}</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>초동조치 기한</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>{{initial_action_due_at}}</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="13" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>문서상태</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>{{alert_status}}</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>최종대책 기한</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>{{final_action_due_at}}</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="13" t="n"/>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>협조 부서</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>{{support_teams}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="6" customHeight="1"/>
+    <row r="9" ht="23" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="001F3864"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">  {{alert_status}}  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00E8ECF2"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">   채울 칸 6개   </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00FFD166"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">①  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00FFD166"/>
+              <sz val="9"/>
+            </rPr>
+            <t>{{due_initial}}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00E8ECF2"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">   ②~⑥ 각 칸 기한</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <color rgb="00A9B6C6"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">   현황·분석은 채워져 있습니다</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>1.  불량 현황        시스템 자동 집계 · 수정 금지</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="13" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>대상 부품</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>{{part_id}} · {{part_name}}</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>불량 유형</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>{{defect_type}}</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="13" t="n"/>
-    </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>집계 기간</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>{{period_start}} ~ {{period_end}}</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>{{period_start}} ~ {{period_end}} ({{window_days}}일 / {{evaluation_mode}})</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>레시피 버전</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>{{source_recipe_version}}</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>검사 수량</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>불량 수량</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>기준 불량률</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>실제 불량률</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>기준 대비</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>실제 PPM</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>완제품 영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>{{inspected_quantity}}</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>{{defective_quantity}}</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>{{threshold_rate}}</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>{{defect_rate}}</t>
+        </is>
+      </c>
+      <c r="E13" s="14">
+        <f>IFERROR(D13/C13,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="15">
+        <f>IFERROR(D13*1000000,"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>{{unit_impact}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>발생 집중</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>{{hotspot}}</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>직전 기간 대비</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>{{trend_vs_prev}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>불량 현상</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>{{phenomenon}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1"/>
+    <row r="17" ht="19" customHeight="1"/>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>2.  시스템이 먼저 본 것        담당자가 확인할 순서대로 · 근거 시트를 함께 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>자동 분석</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>{{auto_analysis}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1"/>
+    <row r="21" ht="19" customHeight="1"/>
+    <row r="22" ht="19" customHeight="1"/>
+    <row r="23" ht="12" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>근거는 별지에 있습니다   ·   「근거」 유닛·슬롯·이미지   |   「판단자료」 추세·레시피·과거 이력·체크리스트   |   「대체품」 후보 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>3.  담당자 작성        아래 크림색 칸만 채우시면 됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">①
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">초동 조치
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="009C2A2A"/>
+              <sz val="8"/>
+            </rPr>
+            <t>{{due_initial}}</t>
+          </r>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>협조 필요    ☐ 생산 중단    ☐ 출하 보류    ☐ 재고 선별    ☐ 고객 통보    ☐ 설비 정지</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1"/>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">②
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">발생 원인
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00808080"/>
+              <sz val="8"/>
+            </rPr>
+            <t>{{due_cause}}</t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1"/>
+    <row r="31" ht="18" customHeight="1"/>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">③
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">유출 원인
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00808080"/>
+              <sz val="8"/>
+            </rPr>
+            <t>{{due_cause}}</t>
+          </r>
+        </is>
+      </c>
+      <c r="B32" s="24" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1"/>
+    <row r="34" ht="18" customHeight="1"/>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">④
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">재발방지
+대책
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00808080"/>
+              <sz val="8"/>
+            </rPr>
+            <t>{{due_action}}</t>
+          </r>
+        </is>
+      </c>
+      <c r="B35" s="24" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1"/>
+    <row r="37" ht="18" customHeight="1"/>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">⑤
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00262626"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">효과 검증
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00808080"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t>{{due_verify}}</t>
+          </r>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>검증 기간</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>적용 레시피</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>검증 수량</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>불량 수량</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>{{defective_quantity}}</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="13" t="n"/>
-    </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>기준 불량률</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>{{threshold_rate}}</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>실제 불량률</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>{{defect_rate}}</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="13" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>초과폭</t>
-        </is>
-      </c>
-      <c r="B13" s="19">
-        <f>IFERROR(MAX(F12-B12,0)*100,"")</f>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>검증 불량률</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="B39" s="25" t="n"/>
+      <c r="D39" s="25" t="n"/>
+      <c r="E39" s="26" t="n"/>
+      <c r="F39" s="26" t="n"/>
+      <c r="G39" s="27">
+        <f>IFERROR(F39/E39,"")</f>
         <v/>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>최초 초과 시각</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>{{first_exceeded_at}}</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>발생 집중</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>{{hotspot}}</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>직전 기간 대비</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>{{trend_vs_prev}}</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="13" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>불량 현상</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>{{phenomenon}}</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="13" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="21" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="13" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="21" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>자동 분석</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>{{auto_analysis}}</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="21" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="13" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>별  지</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>「근거」 유닛·슬롯·이미지   |   「판단자료」 추세 · 레시피 변경 · 과거 이력 · 체크리스트   |   「대체품」 후보 비교</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="13" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>2.  담당자 작성        ① → 초동조치 기한까지   ·   ②~⑥ → 최종대책 기한까지</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="13" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>①
-초동 조치
-(당일)</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>격리·선별·출하보류 범위와 완료 시각. 영향 받는 job_id / unit_id 범위를 함께 적는다. 원인이 안 나와도 당일 회신한다 — 여기는 막았는지만 쓰는 칸이다.</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="13" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="21" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="13" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="21" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>②
-발생 원인</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>왜 만들어졌는가. 「판단자료」 A·B로 시점과 레시피 변경을 대조하고, 재현 또는 실물 확인으로 검증한 근거를 적는다. 가설이면 가설이라고 표시한다.</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="13" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="21" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="21" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="13" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>③
-유출 원인</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>왜 검사에서 걸리지 않았는가. 「판단자료」 D의 검사 항목과 대조해 판정 기준의 한계를 적는다.</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="21" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="13" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="21" t="n"/>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="13" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>④
-재발방지
-대책</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>원인을 제거하는 영구대책. 레시피·공정조건을 바꾸면 변경 후 recipe_version을, 부품을 바꾸면 「대체품」 시트의 대체코드를 적는다. 동일 부품을 쓰는 다른 슬롯으로의 수평전개 여부 포함.</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="13" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="21" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="13" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="21" t="n"/>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="13" t="n"/>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>⑤
-효과 검증</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr">
-        <is>
-          <t>검증 기간</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="26" t="inlineStr">
-        <is>
-          <t>적용 레시피</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
-        <is>
-          <t>검증 수량</t>
-        </is>
-      </c>
-      <c r="F34" s="26" t="inlineStr">
-        <is>
-          <t>불량 수량</t>
-        </is>
-      </c>
-      <c r="G34" s="26" t="inlineStr">
-        <is>
-          <t>검증 불량률</t>
-        </is>
-      </c>
-      <c r="H34" s="27" t="inlineStr">
-        <is>
-          <t>판정</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="21" t="n"/>
-      <c r="B35" s="28" t="inlineStr"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="28" t="inlineStr"/>
-      <c r="E35" s="29" t="inlineStr"/>
-      <c r="F35" s="29" t="inlineStr"/>
-      <c r="G35" s="30">
-        <f>IFERROR(F35/E35,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="31" t="inlineStr">
+      <c r="H39" s="25" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="21" t="n"/>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>대책 적용 후 재집계 결과와 판정 근거. 기준 불량률 이하로 내려오지 않으면 INEFFECTIVE로 두고 ②로 되돌아간다.</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="13" t="n"/>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>⑥ 종결 판정</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="24" t="n"/>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>⑥  종결 판정        잔여 위험을 확인하고 닫습니다</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>종결일</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="13" t="n"/>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="F41" s="25" t="n"/>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>종결 의견</t>
         </is>
       </c>
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t>잔여 위험과 종결 승인 의견.</t>
-        </is>
-      </c>
-      <c r="C38" s="34" t="n"/>
-      <c r="D38" s="34" t="n"/>
-      <c r="E38" s="34" t="n"/>
-      <c r="F38" s="34" t="n"/>
-      <c r="G38" s="34" t="n"/>
-      <c r="H38" s="35" t="n"/>
-    </row>
-    <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="36" t="inlineStr">
-        <is>
-          <t>자동 발행: MAIN_SERVER/scan_quality.py   ·   회색 이탤릭 안내문은 작성 시 지우고 입력   ·   결재 대상은 이 시트 1장</t>
+      <c r="B42" s="24" t="n"/>
+    </row>
+    <row r="43" ht="12" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>자동 발행: MAIN_SERVER/scan_quality.py   ·   회신 칸은 클릭하면 작성 요령이 뜬다   ·   결재 대상은 이 시트 1장</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="43">
+    <mergeCell ref="A9:H9"/>
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="F5:H5"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="B18:H19"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A38:A40"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="B15:H17"/>
-    <mergeCell ref="B20:H20"/>
     <mergeCell ref="H2:H3"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="B26:H28"/>
+    <mergeCell ref="B35:H37"/>
     <mergeCell ref="A15:A17"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B32:H34"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B25:H27"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="B31:H33"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="B19:H22"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A1:D3"/>
     <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B22:H24"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="E1:E3"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A19:A22"/>
     <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F10:H10"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B29:H31"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="B12:D12"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B28:H30"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="F9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"MISSING (미삽입),POSITION_ERROR (위치이상),ORIENTATION_ERROR (방향이상),CRACK (균열)"</formula1>
+  <dataValidations count="15">
+    <dataValidation sqref="F6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK" promptTitle="불량 유형" prompt="CRACK 만 「대체품」 시트가 첨부된다.&#10;MISSING · POSITION_ERROR · ORIENTATION_ERROR 는 조립 불량이라 대체품이 대책이 되지 않는다." type="list">
+      <formula1>"MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ISSUED (발행),ASSIGNED (배정),IN_PROGRESS (조치중),VERIFYING (검증중),CLOSED (종결)"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ISSUED (발행),ASSIGNED (배정),IN_PROGRESS (조치중),VERIFYING (검증중),CLOSED (종결)"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H39" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: PENDING,EFFECTIVE,INEFFECTIVE" promptTitle="⑤ 판정" prompt="기준 불량률 이하면 EFFECTIVE · 아니면 INEFFECTIVE로 두고 ②로 되돌아간다." type="list">
       <formula1>"PENDING,EFFECTIVE,INEFFECTIVE"</formula1>
     </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 협조가 필요한 조치" prompt="담당자 혼자 결정할 수 없는 항목이다. 해당하는 것의 ☐ 를 ☑ 로 바꾸고,&#10;아래 칸에 누구에게 언제 요청했는지 적는다.&#10;&#10;생산 중단 → 생산팀장 · 출하 보류 → 영업/물류 · 재고 선별 → 인력 투입 승인&#10;고객 통보 → 품질보증 책임자 · 설비 정지 → 설비팀&#10;→ containment_summary 첫 줄로 함께 저장된다"/>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 초동 조치 — 오늘 안에" prompt="격리·선별·출하보류 범위와 완료 시각을 적는다.&#10;영향 받는 job_id / unit_id 범위를 함께 적는다.&#10;&#10;원인이 안 나와도 오늘 회신한다. 여기는 '막았는지'만 쓰는 칸이다.&#10;원인을 없애는 것은 ④ 이고, 이 칸은 확산을 멈추는 칸이다.&#10;→ alert_countermeasures.containment_summary"/>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 왜 만들어졌는가" prompt="「판단자료」 A·B로 급증 시점과 레시피 변경 시점을 대조한다.&#10;재현 또는 실물 확인으로 검증한 근거를 적는다.&#10;가설이면 '가설'이라고 표시한다.&#10;→ alert_countermeasures.root_cause_summary"/>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="③ 유출 원인 — 왜 검사에서 걸리지 않았는가" prompt="「판단자료」 D의 검사 항목과 대조해 판정 기준의 한계를 적는다.&#10;검사를 안 한 것인지, 했는데 못 걸른 것인지 구분한다.&#10;→ alert_countermeasures.escape_cause_summary"/>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="④ 재발방지 대책 — 원인을 제거하는 영구대책" prompt="레시피·공정조건을 바꾸면 변경 후 recipe_version을 적는다.&#10;부품을 바꾸면 「대체품」 시트의 대체코드를 적는다.&#10;동일 부품을 쓰는 다른 슬롯으로의 수평전개 여부를 포함한다.&#10;&#10;레시피 변경은 변경관리 승인이, 부품 교체는 고객 승인이 필요할 수 있다.&#10;승인 절차가 걸리면 그 일정도 함께 적는다.&#10;→ alert_countermeasures.applied_recipe_version / applied_at"/>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 기간" prompt="대책을 적용하고 다시 집계한 구간. [시작, 끝) 으로 적는다.&#10;검증 물량이 기준 최소 건수를 넘어야 판정할 수 있다."/>
+    <dataValidation sqref="D39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 적용 레시피" prompt="대책을 적용한 뒤 실행한 recipe_version.&#10;이 값이 있어야 적용 전후를 같은 제품 안에서 비교할 수 있다.&#10;→ alert_countermeasures.applied_recipe_version"/>
+    <dataValidation sqref="E39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 검사 수량" prompt="부품 기준 검사 건수 (유닛 수 × 해당 부품 슬롯 수).&#10;→ alert_countermeasures.verified_inspected_quantity"/>
+    <dataValidation sqref="F39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 불량 수량" prompt="→ alert_countermeasures.verified_defective_quantity"/>
+    <dataValidation sqref="H39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정" prompt="기준 불량률 이하로 내려왔으면 EFFECTIVE.&#10;아니면 INEFFECTIVE로 두고 ②로 되돌아간다.&#10;→ alert_countermeasures.verification_status"/>
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정 근거" prompt="재집계 결과를 그렇게 읽은 이유.&#10;검증 수량이 기준 최소 건수에 못 미치면 그것도 적는다."/>
+    <dataValidation sqref="F41" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결일" prompt="→ alerts.closed_at · alert_status='CLOSED'"/>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결 의견" prompt="잔여 위험과 종결 승인 의견.&#10;→ alert_countermeasures.closure_note / closed_by"/>
   </dataValidations>
-  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;9&amp;K808080{{alert_code}}&amp;R&amp;9&amp;K808080&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1548,134 +1495,134 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>발행 시점 고정 근거        [발행 시점 고정]</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>defect_report.alert_evidence 스냅샷 · 문서번호 {{alert_code}} · 수정 금지</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>슬롯별 발생 분포        어느 슬롯에 몰려 있는지 · 공정 원인 판단의 1차 근거</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>슬롯</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>불량 건수</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>슬롯 불량률</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n"/>
+      <c r="E4" s="32" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>{{slot_code}}</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>{{count}}</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>{{slot_rate}}</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>{{note}}</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>{{slot_note}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>불량 유닛 목록</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>unit_id</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>슬롯</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>불량 유형</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>검사 시각</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>검사 이미지 경로</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>{{unit_id}}</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>{{slot_code}}</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>{{defect_type}}</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>{{inspected_at}}</t>
         </is>
       </c>
-      <c r="E9" s="41" t="inlineStr">
+      <c r="E9" s="34" t="inlineStr">
         <is>
           <t>{{inspection_image_path}}</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <mergeCells count="6">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A7:E7"/>
@@ -1684,7 +1631,7 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -1698,7 +1645,7 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -1709,389 +1656,368 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>판단 자료</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="38" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>담당자가 ②발생 원인 · ③유출 원인을 좁히는 데 쓰는 참고 자료 · 자동 조회 · 결재 대상 아님</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>판단 순서    ①「근거」어느 슬롯에 몰렸나  →  ② A 언제부터 올랐나  →  ③ B 그때 무엇이 바뀌었나  →  ④ C 전에도 있었나  →  ⑤ D 무엇을 확인하나</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>A.  주차별 추세        [발행 시점 고정]</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
-        <is>
-          <t>언제부터 올라갔는지 · 급변 시점과 아래 B의 레시피 변경 시점을 대조한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>언제부터 올라갔는지 · 급변 시점과 아래 B의 레시피 변경 시점을 대조한다. 주차 경계와 대책서 집계 구간은 일치하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>주차</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>검사 수량</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>불량 수량</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="31" t="inlineStr">
         <is>
           <t>불량률</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>기준 대비</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="31" t="inlineStr">
         <is>
           <t>레시피</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n"/>
+      <c r="H7" s="32" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>{{week}}</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>{{inspected}}</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>{{defective}}</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>{{rate}}</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>{{vs_threshold}}</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>{{recipe_version}}</t>
         </is>
       </c>
-      <c r="G8" s="44" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>{{note}}</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n"/>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>B.  레시피 변경 전후 불량률        [발행 시점 고정]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="43" t="inlineStr">
-        <is>
-          <t>조회 8 · 공정 조건이 원인인지 부품이 원인인지 가르는 1차 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>datastation_part_rates · 공정 조건이 원인인지 부품이 원인인지 가르는 1차 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>레시피</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>적용 기간</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>검사 수량</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>불량 수량</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>불량률</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="31" t="inlineStr">
         <is>
           <t>기준 대비</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="31" t="inlineStr">
         <is>
           <t>변경 내용</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n"/>
+      <c r="H12" s="32" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>{{recipe_version}}</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>{{applied_period}}</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>{{inspected}}</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>{{defective}}</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>{{rate}}</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>{{vs_threshold}}</t>
         </is>
       </c>
-      <c r="G13" s="44" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>{{change_note}}</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>C.  동일 부품 · 동일 유형 과거 대책서        [발행 시점 고정]</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>재발이면 이전 대책이 왜 듣지 않았는지부터 확인한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>datastation_alerts · 재발이면 이전 대책이 왜 듣지 않았는지부터 확인한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>문서번호</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>집계 기간</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>불량률</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>적용 대책</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="31" t="inlineStr">
         <is>
           <t>당시 근본 원인</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="H17" s="32" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>{{alert_code}}</t>
         </is>
       </c>
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>{{period}}</t>
         </is>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>{{defect_rate}}</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="38" t="inlineStr">
         <is>
           <t>{{alert_status}}</t>
         </is>
       </c>
-      <c r="E18" s="44" t="inlineStr">
-        <is>
-          <t>{{applied_recipe_version}}</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="44" t="inlineStr">
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>{{applied_recipe_version}} / {{applied_at}}</t>
+        </is>
+      </c>
+      <c r="G18" s="37" t="inlineStr">
         <is>
           <t>{{root_cause_summary}}</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>D.  품질 체크리스트        [조회 시점 참조 · 데이터시트 갱신 시 바뀜]</t>
         </is>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>part_catalog.quality_checklists · 이 범주에서 무엇을 확인해야 하는지</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>datastation_part_checklist · part_catalog.quality_checklists.category = part_groups.category_label · 이 범주에서 무엇을 확인해야 하는지</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="31" t="inlineStr">
         <is>
           <t>확인 항목</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="C22" s="41" t="n"/>
+      <c r="D22" s="32" t="n"/>
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>이상 시 조치</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="F22" s="41" t="n"/>
+      <c r="G22" s="41" t="n"/>
+      <c r="H22" s="32" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>입고 검사</t>
         </is>
       </c>
-      <c r="B23" s="44" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>{{incoming_inspection}}</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="44" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>{{action_on_anomaly}}</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>조립·보관</t>
         </is>
       </c>
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>{{assembly_control}}</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="44" t="inlineStr"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="45" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>기능·신뢰성</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>{{reliability_test}}</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="44" t="inlineStr"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
+  <mergeCells count="25">
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="E25:H25"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="E17:F17"/>
@@ -2102,24 +2028,20 @@
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G18:H18"/>
-    <mergeCell ref="E24:H24"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="E23:H23"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E23:H25"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="E18:F18"/>
   </mergeCells>
-  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="14" min="0" max="16383" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>
 
@@ -2143,126 +2065,126 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>대체품 후보        [조회 시점 참조]</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="38" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>불량유형이 CRACK일 때만 첨부된다 · MISSING · POSITION_ERROR · ORIENTATION_ERROR는 조립 불량이므로 대체품이 대책이 되지 않는다</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="46" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>동일 정격만으로 drop-in 판단 금지 · 「필수 재검증」을 모두 통과하고 변경 승인이 완료된 뒤에만 적용한다.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
-        <is>
-          <t>조회 시각 {{queried_at}}   ·   데이터시트 {{source_file}} (기준일 {{source_dated_on}})   ·   Group ID {{group_id}}   ·   후보 {{candidate_count}}종   ·   행은 후보 수만큼 반복</t>
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>조회 시각 {{queried_at}}   ·   데이터시트 {{source_file}} (기준일 {{source_dated_on}})   ·   Group ID {{group_id}} ({{category_label}})   ·   후보 {{candidate_count}}종   ·   행은 후보 수만큼 반복</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>대체코드</t>
         </is>
       </c>
-      <c r="C6" s="48" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>제조사 / P/N</t>
         </is>
       </c>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>핵심 사양·용도</t>
         </is>
       </c>
-      <c r="E6" s="48" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>상호호환 상태</t>
         </is>
       </c>
-      <c r="F6" s="48" t="inlineStr">
+      <c r="F6" s="31" t="inlineStr">
         <is>
           <t>필수 재검증</t>
         </is>
       </c>
-      <c r="G6" s="48" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t>{{defect_type}} 관련 소견</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="31" t="inlineStr">
         <is>
           <t>Source · 확인일</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="45" t="inlineStr">
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>{{candidate_role}}</t>
         </is>
       </c>
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>{{alternate_code}}</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>{{manufacturer}} / {{manufacturer_part_number}}</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>{{key_spec}}</t>
         </is>
       </c>
-      <c r="E7" s="45" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>{{compatibility_status}}</t>
         </is>
       </c>
-      <c r="F7" s="49" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>{{revalidation_items}}</t>
         </is>
       </c>
-      <c r="G7" s="49" t="inlineStr">
+      <c r="G7" s="37" t="inlineStr">
         <is>
           <t>{{defect_relevance}}</t>
         </is>
       </c>
-      <c r="H7" s="49" t="inlineStr">
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>{{source_id}} · {{checked_at}}</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>단가·MOQ·재고·리드타임·공급사는 이 문서에 싣지 않는다. 조회 시점에 이미 상하는 값이고 품질 담당자의 결정 변수가 아니다 → GET /parts/{part_id} 또는 구매 담당</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:H7"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <mergeCells count="5">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
@@ -2270,7 +2192,7 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
+++ b/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
@@ -8,25 +8,28 @@
   </bookViews>
   <sheets>
     <sheet name="대책서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="근거" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="판단자료" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="대체품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="검증" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="근거" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="판단자료" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="대체품" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="reply_containment_scope">'대책서'!$B$25</definedName>
-    <definedName name="reply_containment">'대책서'!$B$26</definedName>
-    <definedName name="reply_root_cause">'대책서'!$B$29</definedName>
-    <definedName name="reply_escape_cause">'대책서'!$B$32</definedName>
-    <definedName name="reply_prevention">'대책서'!$B$35</definedName>
-    <definedName name="reply_verify_period">'대책서'!$B$39</definedName>
-    <definedName name="reply_verify_recipe">'대책서'!$D$39</definedName>
-    <definedName name="reply_verify_inspected">'대책서'!$E$39</definedName>
-    <definedName name="reply_verify_defective">'대책서'!$F$39</definedName>
-    <definedName name="reply_verify_status">'대책서'!$H$39</definedName>
-    <definedName name="reply_verify_note">'대책서'!$B$40</definedName>
-    <definedName name="reply_closed_at">'대책서'!$F$41</definedName>
-    <definedName name="reply_closure_note">'대책서'!$B$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$H$43</definedName>
+    <definedName name="reply_containment_scope">'대책서'!$B$21</definedName>
+    <definedName name="reply_containment">'대책서'!$B$22</definedName>
+    <definedName name="reply_root_cause_label">'대책서'!$B$25</definedName>
+    <definedName name="reply_root_cause">'대책서'!$B$26</definedName>
+    <definedName name="reply_escape_cause">'대책서'!$B$28</definedName>
+    <definedName name="reply_prevention">'대책서'!$B$31</definedName>
+    <definedName name="reply_verify_period">'검증'!$B$5</definedName>
+    <definedName name="reply_verify_recipe">'검증'!$D$5</definedName>
+    <definedName name="reply_verify_inspected">'검증'!$E$5</definedName>
+    <definedName name="reply_verify_defective">'검증'!$F$5</definedName>
+    <definedName name="reply_verify_status">'검증'!$H$5</definedName>
+    <definedName name="reply_verify_note">'검증'!$B$6</definedName>
+    <definedName name="reply_closed_at">'검증'!$F$8</definedName>
+    <definedName name="reply_closure_note">'검증'!$B$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'검증'!$A$1:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,12 +37,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.000%"/>
-    <numFmt numFmtId="165" formatCode="0.0&quot;배&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot; PPM&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0&quot;배&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,9 +51,14 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="00262626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00262626"/>
-      <sz val="17"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -64,11 +71,6 @@
       <b val="1"/>
       <color rgb="00262626"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00262626"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -85,23 +87,13 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00262626"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00808080"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="009C2A2A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00262626"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -127,11 +119,6 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00808080"/>
-      <sz val="7.5"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00808080"/>
       <sz val="8"/>
@@ -140,6 +127,22 @@
       <name val="맑은 고딕"/>
       <color rgb="00262626"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00808080"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00595959"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00262626"/>
+      <sz val="7.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -152,11 +155,6 @@
       <b val="1"/>
       <color rgb="009C2A2A"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00595959"/>
-      <sz val="7.5"/>
     </font>
   </fonts>
   <fills count="10">
@@ -278,27 +276,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -313,103 +314,92 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="1" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -780,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -794,101 +784,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>불  량  대  책  서</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>결
 재</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>작성</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>검토</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>승인</t>
         </is>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1">
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
     </row>
     <row r="3" ht="17" customHeight="1"/>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>문서번호</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>{{alert_code}}</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>발행일시</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>{{issued_at}}</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>대상 부품</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>{{part_id}} · {{part_name}} ({{group_id}} / {{category_label}})</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>불량 유형</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>{{defect_type}}</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>주관 담당</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>{{assignee}}</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>협조 부서</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>{{support_teams}}</t>
         </is>
@@ -896,7 +887,7 @@
     </row>
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="23" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -910,10 +901,10 @@
           <r>
             <rPr>
               <rFont val="맑은 고딕"/>
-              <color rgb="00E8ECF2"/>
-              <sz val="8"/>
+              <color rgb="00A9B6C6"/>
+              <sz val="7.5"/>
             </rPr>
-            <t xml:space="preserve">   채울 칸 6개   </t>
+            <t xml:space="preserve">   회신 기한   </t>
           </r>
           <r>
             <rPr>
@@ -940,7 +931,34 @@
               <color rgb="00E8ECF2"/>
               <sz val="8"/>
             </rPr>
-            <t xml:space="preserve">   ②~⑥ 각 칸 기한</t>
+            <t xml:space="preserve">     ②③  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00E8ECF2"/>
+              <sz val="8"/>
+            </rPr>
+            <t>{{due_cause}}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00E8ECF2"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">     ④  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="맑은 고딕"/>
+              <b val="1"/>
+              <color rgb="00E8ECF2"/>
+              <sz val="8"/>
+            </rPr>
+            <t>{{due_action}}</t>
           </r>
           <r>
             <rPr>
@@ -948,186 +966,147 @@
               <color rgb="00A9B6C6"/>
               <sz val="7.5"/>
             </rPr>
-            <t xml:space="preserve">   현황·분석은 채워져 있습니다</t>
+            <t xml:space="preserve">     ⑤⑥ 「검증」 시트</t>
           </r>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>1.  불량 현황        시스템 자동 집계 · 수정 금지</t>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>1.  불량 현황</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>집계 기간</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>{{period_start}} ~ {{period_end}} ({{window_days}}일 / {{evaluation_mode}})</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>레시피 버전</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>{{source_recipe_version}}</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>검사 수량</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>불량 수량</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>기준 불량률</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>실제 불량률</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>실제 PPM (기준 {{threshold_ppm}})</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>기준 대비</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>실제 PPM</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>완제품 영향</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>{{inspected_quantity}}</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>{{defective_quantity}}</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>{{threshold_rate}}</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>{{defect_rate}}</t>
-        </is>
-      </c>
-      <c r="E13" s="14">
-        <f>IFERROR(D13/C13,"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="15">
-        <f>IFERROR(D13*1000000,"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>{{defect_ppm}}</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>{{vs_threshold_ratio}}</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>{{unit_impact}}</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>발생 집중</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>{{hotspot}}</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>직전 기간 대비</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>{{trend_vs_prev}}</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>불량 현상</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>{{phenomenon}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1"/>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2.  시스템이 먼저 본 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>자동 분석</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>{{auto_analysis}}</t>
+        </is>
+      </c>
+    </row>
     <row r="17" ht="19" customHeight="1"/>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>2.  시스템이 먼저 본 것        담당자가 확인할 순서대로 · 근거 시트를 함께 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>자동 분석</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>{{auto_analysis}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="19" customHeight="1"/>
-    <row r="21" ht="19" customHeight="1"/>
-    <row r="22" ht="19" customHeight="1"/>
-    <row r="23" ht="12" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>근거는 별지에 있습니다   ·   「근거」 유닛·슬롯·이미지   |   「판단자료」 추세·레시피·과거 이력·체크리스트   |   「대체품」 후보 비교</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>3.  담당자 작성        아래 크림색 칸만 채우시면 됩니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="18" ht="19" customHeight="1"/>
+    <row r="19" ht="19" customHeight="1"/>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>3.  담당자 작성</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1146,33 +1125,23 @@
               <color rgb="00262626"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">초동 조치
-</t>
+            <t>초동 조치</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="009C2A2A"/>
-              <sz val="8"/>
-            </rPr>
-            <t>{{due_initial}}</t>
-          </r>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>협조 필요    ☐ 생산 중단    ☐ 출하 보류    ☐ 재고 선별    ☐ 고객 통보    ☐ 설비 정지</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1"/>
-    <row r="28" ht="18" customHeight="1"/>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="20" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1"/>
+    <row r="24" ht="18" customHeight="1"/>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1191,26 +1160,18 @@
               <color rgb="00262626"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">발생 원인
-</t>
+            <t>발생 원인</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00808080"/>
-              <sz val="8"/>
-            </rPr>
-            <t>{{due_cause}}</t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="24" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1"/>
-    <row r="31" ht="18" customHeight="1"/>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+        </is>
+      </c>
+      <c r="B25" s="21" t="n"/>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="B26" s="20" t="n"/>
+    </row>
+    <row r="27" ht="19" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1229,26 +1190,16 @@
               <color rgb="00262626"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">유출 원인
-</t>
+            <t>유출 원인</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00808080"/>
-              <sz val="8"/>
-            </rPr>
-            <t>{{due_cause}}</t>
-          </r>
-        </is>
-      </c>
-      <c r="B32" s="24" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1"/>
-    <row r="34" ht="18" customHeight="1"/>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+        </is>
+      </c>
+      <c r="B28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1"/>
+    <row r="30" ht="18" customHeight="1"/>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1267,27 +1218,123 @@
               <color rgb="00262626"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">재발방지
-대책
-</t>
+            <t>재발방지
+대책</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <b val="1"/>
-              <color rgb="00808080"/>
-              <sz val="8"/>
-            </rPr>
-            <t>{{due_action}}</t>
-          </r>
-        </is>
-      </c>
-      <c r="B35" s="24" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1"/>
-    <row r="37" ht="18" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+        </is>
+      </c>
+      <c r="B31" s="20" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1"/>
+    <row r="33" ht="18" customHeight="1"/>
+    <row r="34" ht="12" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>자동 발행   ·   회신 칸은 클릭하면 작성 요령이 뜬다</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="37">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="B26:H27"/>
+    <mergeCell ref="B1:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B31:H33"/>
+    <mergeCell ref="B22:H24"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="B16:H19"/>
+    <mergeCell ref="B28:H30"/>
+    <mergeCell ref="A34:H34"/>
+  </mergeCells>
+  <dataValidations count="7">
+    <dataValidation sqref="F6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK" promptTitle="불량 유형" prompt="별지 3장은 유형과 무관하게 항상 첨부한다.&#10;어느 자료가 이번 건에 쓸모 있는지는 담당자가 판단한다." type="list">
+      <formula1>"MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 협조가 필요한 조치" prompt="담당자 혼자 결정할 수 없는 항목이다. 해당하는 것의 ☐ 를 ☑ 로 바꾸고,&#10;아래 칸에 누구에게 언제 요청했는지 적는다.&#10;&#10;생산 중단 → 생산팀장 · 출하 보류 → 영업/물류 · 재고 선별 → 인력 투입 승인&#10;고객 통보 → 품질보증 책임자 · 설비 정지 → 설비팀&#10;→ containment_summary 첫 줄로 함께 저장된다"/>
+    <dataValidation sqref="B22" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 초동 조치 — 오늘 안에" prompt="격리·선별·출하보류 범위와 완료 시각을 적는다.&#10;영향 받는 job_id / unit_id 범위를 함께 적는다.&#10;&#10;원인이 안 나와도 오늘 회신한다. 여기는 '막았는지'만 쓰는 칸이다.&#10;원인을 없애는 것은 ④ 이고, 이 칸은 확산을 멈추는 칸이다.&#10;→ alert_countermeasures.containment_summary"/>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 한 줄 요약 (40자)" prompt="아래 본문을 한 줄로 줄인 것. 예: '배치 하강속도 상향 + 지지 핀 최원거리 슬롯'&#10;&#10;이 부품·유형이 다시 나면, 다음 대책서의 자동 분석 ③ 줄이 이 칸을 그대로 읽어&#10;'과거 원인'으로 싣는다. 본문은 길어서 그 자리에 들어가지 않는다.&#10;→ alert_countermeasures.root_cause_label"/>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 왜 만들어졌는가" prompt="「판단자료」 A·B로 급증 시점과 레시피 변경 시점을 대조한다.&#10;재현 또는 실물 확인으로 검증한 근거를 적는다.&#10;가설이면 '가설'이라고 표시한다.&#10;→ alert_countermeasures.root_cause_summary"/>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="③ 유출 원인 — 왜 검사에서 걸리지 않았는가" prompt="「판단자료」 D의 검사 항목과 대조해 판정 기준의 한계를 적는다.&#10;검사를 안 한 것인지, 했는데 못 걸른 것인지 구분한다.&#10;→ alert_countermeasures.escape_cause_summary"/>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="④ 재발방지 대책 — 원인을 제거하는 영구대책" prompt="레시피·공정조건을 바꾸면 변경 후 recipe_version을 적는다.&#10;부품을 바꾸면 「대체품」 시트의 대체코드를 적는다.&#10;동일 부품을 쓰는 다른 슬롯으로의 수평전개 여부를 포함한다.&#10;&#10;레시피 변경은 변경관리 승인이, 부품 교체는 고객 승인이 필요할 수 있다.&#10;승인 절차가 걸리면 그 일정도 함께 적는다.&#10;→ alert_countermeasures.applied_recipe_version / applied_at"/>
+  </dataValidations>
+  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;9&amp;K808080{{alert_code}}&amp;R&amp;9&amp;K808080&amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>5 · 6.  효과 검증과 종결        [담당자 작성]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>{{alert_code}}   ·   {{part_id}} / {{defect_type}}   ·   발행 {{issued_at}}   ·   ④ 적용 후 다시 집계해서 채운다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1320,165 +1367,110 @@
           </r>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>검증 기간</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>적용 레시피</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>검증 수량</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>불량 수량</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>검증 불량률</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="B39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="26" t="n"/>
-      <c r="F39" s="26" t="n"/>
-      <c r="G39" s="27">
-        <f>IFERROR(F39/E39,"")</f>
+    <row r="5" ht="21" customHeight="1">
+      <c r="B5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26">
+        <f>IFERROR(F5/E5,"")</f>
         <v/>
       </c>
-      <c r="H39" s="25" t="inlineStr">
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="24" t="n"/>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>⑥  종결 판정        잔여 위험을 확인하고 닫습니다</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
+    <row r="6" ht="34" customHeight="1">
+      <c r="B6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>⑥  종결 판정</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>종결일</t>
         </is>
       </c>
-      <c r="F41" s="25" t="n"/>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="F8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>종결 의견</t>
         </is>
       </c>
-      <c r="B42" s="24" t="n"/>
-    </row>
-    <row r="43" ht="12" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
-        <is>
-          <t>자동 발행: MAIN_SERVER/scan_quality.py   ·   회신 칸은 클릭하면 작성 요령이 뜬다   ·   결재 대상은 이 시트 1장</t>
-        </is>
-      </c>
-    </row>
+      <c r="B9" s="20" t="n"/>
+    </row>
+    <row r="10" ht="12" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="43">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="B15:H17"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="B26:H28"/>
-    <mergeCell ref="B35:H37"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="B32:H34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="B19:H22"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A1:D3"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B29:H31"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="G2:G3"/>
+  <mergeCells count="9">
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
-  <dataValidations count="15">
-    <dataValidation sqref="F6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK" promptTitle="불량 유형" prompt="CRACK 만 「대체품」 시트가 첨부된다.&#10;MISSING · POSITION_ERROR · ORIENTATION_ERROR 는 조립 불량이라 대체품이 대책이 되지 않는다." type="list">
-      <formula1>"MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H39" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: PENDING,EFFECTIVE,INEFFECTIVE" promptTitle="⑤ 판정" prompt="기준 불량률 이하면 EFFECTIVE · 아니면 INEFFECTIVE로 두고 ②로 되돌아간다." type="list">
+  <dataValidations count="9">
+    <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: PENDING,EFFECTIVE,INEFFECTIVE" promptTitle="⑤ 판정" prompt="기준 불량률 이하면 EFFECTIVE · 아니면 INEFFECTIVE로 두고 ②로 되돌아간다." type="list">
       <formula1>"PENDING,EFFECTIVE,INEFFECTIVE"</formula1>
     </dataValidation>
-    <dataValidation sqref="B25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 협조가 필요한 조치" prompt="담당자 혼자 결정할 수 없는 항목이다. 해당하는 것의 ☐ 를 ☑ 로 바꾸고,&#10;아래 칸에 누구에게 언제 요청했는지 적는다.&#10;&#10;생산 중단 → 생산팀장 · 출하 보류 → 영업/물류 · 재고 선별 → 인력 투입 승인&#10;고객 통보 → 품질보증 책임자 · 설비 정지 → 설비팀&#10;→ containment_summary 첫 줄로 함께 저장된다"/>
-    <dataValidation sqref="B26" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 초동 조치 — 오늘 안에" prompt="격리·선별·출하보류 범위와 완료 시각을 적는다.&#10;영향 받는 job_id / unit_id 범위를 함께 적는다.&#10;&#10;원인이 안 나와도 오늘 회신한다. 여기는 '막았는지'만 쓰는 칸이다.&#10;원인을 없애는 것은 ④ 이고, 이 칸은 확산을 멈추는 칸이다.&#10;→ alert_countermeasures.containment_summary"/>
-    <dataValidation sqref="B29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 왜 만들어졌는가" prompt="「판단자료」 A·B로 급증 시점과 레시피 변경 시점을 대조한다.&#10;재현 또는 실물 확인으로 검증한 근거를 적는다.&#10;가설이면 '가설'이라고 표시한다.&#10;→ alert_countermeasures.root_cause_summary"/>
-    <dataValidation sqref="B32" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="③ 유출 원인 — 왜 검사에서 걸리지 않았는가" prompt="「판단자료」 D의 검사 항목과 대조해 판정 기준의 한계를 적는다.&#10;검사를 안 한 것인지, 했는데 못 걸른 것인지 구분한다.&#10;→ alert_countermeasures.escape_cause_summary"/>
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="④ 재발방지 대책 — 원인을 제거하는 영구대책" prompt="레시피·공정조건을 바꾸면 변경 후 recipe_version을 적는다.&#10;부품을 바꾸면 「대체품」 시트의 대체코드를 적는다.&#10;동일 부품을 쓰는 다른 슬롯으로의 수평전개 여부를 포함한다.&#10;&#10;레시피 변경은 변경관리 승인이, 부품 교체는 고객 승인이 필요할 수 있다.&#10;승인 절차가 걸리면 그 일정도 함께 적는다.&#10;→ alert_countermeasures.applied_recipe_version / applied_at"/>
-    <dataValidation sqref="B39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 기간" prompt="대책을 적용하고 다시 집계한 구간. [시작, 끝) 으로 적는다.&#10;검증 물량이 기준 최소 건수를 넘어야 판정할 수 있다."/>
-    <dataValidation sqref="D39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 적용 레시피" prompt="대책을 적용한 뒤 실행한 recipe_version.&#10;이 값이 있어야 적용 전후를 같은 제품 안에서 비교할 수 있다.&#10;→ alert_countermeasures.applied_recipe_version"/>
-    <dataValidation sqref="E39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 검사 수량" prompt="부품 기준 검사 건수 (유닛 수 × 해당 부품 슬롯 수).&#10;→ alert_countermeasures.verified_inspected_quantity"/>
-    <dataValidation sqref="F39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 불량 수량" prompt="→ alert_countermeasures.verified_defective_quantity"/>
-    <dataValidation sqref="H39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정" prompt="기준 불량률 이하로 내려왔으면 EFFECTIVE.&#10;아니면 INEFFECTIVE로 두고 ②로 되돌아간다.&#10;→ alert_countermeasures.verification_status"/>
-    <dataValidation sqref="B40" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정 근거" prompt="재집계 결과를 그렇게 읽은 이유.&#10;검증 수량이 기준 최소 건수에 못 미치면 그것도 적는다."/>
-    <dataValidation sqref="F41" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결일" prompt="→ alerts.closed_at · alert_status='CLOSED'"/>
-    <dataValidation sqref="B42" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결 의견" prompt="잔여 위험과 종결 승인 의견.&#10;→ alert_countermeasures.closure_note / closed_by"/>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 기간" prompt="대책을 적용하고 다시 집계한 구간. [시작, 끝) 으로 적는다.&#10;검증 물량이 기준 최소 건수를 넘어야 판정할 수 있다."/>
+    <dataValidation sqref="D5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 적용 레시피" prompt="대책을 적용한 뒤 실행한 recipe_version.&#10;이 값이 있어야 적용 전후를 같은 제품 안에서 비교할 수 있다.&#10;→ alert_countermeasures.applied_recipe_version"/>
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 검사 수량" prompt="부품 기준 검사 건수 (유닛 수 × 해당 부품 슬롯 수).&#10;→ alert_countermeasures.verified_inspected_quantity"/>
+    <dataValidation sqref="F5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 불량 수량" prompt="→ alert_countermeasures.verified_defective_quantity"/>
+    <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정" prompt="기준 불량률 이하로 내려왔으면 EFFECTIVE.&#10;아니면 INEFFECTIVE로 두고 ②로 되돌아간다.&#10;→ alert_countermeasures.verification_status"/>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정 근거" prompt="재집계 결과를 그렇게 읽은 이유.&#10;검증 수량이 기준 최소 건수에 못 미치면 그것도 적는다."/>
+    <dataValidation sqref="F8" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결일" prompt="→ alerts.closed_at · alert_status='CLOSED'"/>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결 의견" prompt="잔여 위험과 종결 승인 의견.&#10;→ alert_countermeasures.closure_note / closed_by"/>
   </dataValidations>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;9&amp;K808080{{alert_code}}&amp;R&amp;9&amp;K808080&amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1495,127 +1487,127 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>발행 시점 고정 근거        [발행 시점 고정]</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>defect_report.alert_evidence 스냅샷 · 문서번호 {{alert_code}} · 수정 금지</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>슬롯별 발생 분포        어느 슬롯에 몰려 있는지 · 공정 원인 판단의 1차 근거</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>슬롯</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>불량 건수</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>슬롯 불량률</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="E4" s="32" t="n"/>
+      <c r="E4" s="30" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>{{slot_code}}</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>{{count}}</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>{{slot_rate}}</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>{{slot_note}}</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>불량 유닛 목록</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>unit_id</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>슬롯</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>불량 유형</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>검사 시각</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>검사 이미지 경로</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>{{unit_id}}</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>{{slot_code}}</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>{{defect_type}}</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>{{inspected_at}}</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>{{inspection_image_path}}</t>
         </is>
@@ -1636,7 +1628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1656,356 +1648,356 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>판단 자료</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>담당자가 ②발생 원인 · ③유출 원인을 좁히는 데 쓰는 참고 자료 · 자동 조회 · 결재 대상 아님</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>판단 순서    ①「근거」어느 슬롯에 몰렸나  →  ② A 언제부터 올랐나  →  ③ B 그때 무엇이 바뀌었나  →  ④ C 전에도 있었나  →  ⑤ D 무엇을 확인하나</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>A.  주차별 추세        [발행 시점 고정]</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>언제부터 올라갔는지 · 급변 시점과 아래 B의 레시피 변경 시점을 대조한다. 주차 경계와 대책서 집계 구간은 일치하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>주차</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>검사 수량</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>불량 수량</t>
         </is>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>불량률</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>기준 대비</t>
         </is>
       </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>레시피</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="H7" s="32" t="n"/>
+      <c r="H7" s="30" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>{{week}}</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>{{inspected}}</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>{{defective}}</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>{{rate}}</t>
         </is>
       </c>
-      <c r="E8" s="36" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>{{vs_threshold}}</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>{{recipe_version}}</t>
         </is>
       </c>
-      <c r="G8" s="34" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>{{note}}</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>B.  레시피 변경 전후 불량률        [발행 시점 고정]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>datastation_part_rates · 공정 조건이 원인인지 부품이 원인인지 가르는 1차 근거</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>레시피</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>적용 기간</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>검사 수량</t>
         </is>
       </c>
-      <c r="D12" s="31" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>불량 수량</t>
         </is>
       </c>
-      <c r="E12" s="31" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>불량률</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>기준 대비</t>
         </is>
       </c>
-      <c r="G12" s="31" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t>변경 내용</t>
         </is>
       </c>
-      <c r="H12" s="32" t="n"/>
+      <c r="H12" s="30" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>{{recipe_version}}</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>{{applied_period}}</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>{{inspected}}</t>
         </is>
       </c>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>{{defective}}</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>{{rate}}</t>
         </is>
       </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="F13" s="34" t="inlineStr">
         <is>
           <t>{{vs_threshold}}</t>
         </is>
       </c>
-      <c r="G13" s="37" t="inlineStr">
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>{{change_note}}</t>
         </is>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>C.  동일 부품 · 동일 유형 과거 대책서        [발행 시점 고정]</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>datastation_alerts · 재발이면 이전 대책이 왜 듣지 않았는지부터 확인한다</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>문서번호</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>집계 기간</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>불량률</t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="E17" s="31" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>적용 대책</t>
         </is>
       </c>
-      <c r="F17" s="32" t="n"/>
-      <c r="G17" s="31" t="inlineStr">
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="29" t="inlineStr">
         <is>
           <t>당시 근본 원인</t>
         </is>
       </c>
-      <c r="H17" s="32" t="n"/>
+      <c r="H17" s="30" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>{{alert_code}}</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>{{period}}</t>
         </is>
       </c>
-      <c r="C18" s="39" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>{{defect_rate}}</t>
         </is>
       </c>
-      <c r="D18" s="38" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>{{alert_status}}</t>
         </is>
       </c>
-      <c r="E18" s="40" t="inlineStr">
+      <c r="E18" s="38" t="inlineStr">
         <is>
           <t>{{applied_recipe_version}} / {{applied_at}}</t>
         </is>
       </c>
-      <c r="G18" s="37" t="inlineStr">
+      <c r="G18" s="35" t="inlineStr">
         <is>
           <t>{{root_cause_summary}}</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>D.  품질 체크리스트        [조회 시점 참조 · 데이터시트 갱신 시 바뀜]</t>
         </is>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>datastation_part_checklist · part_catalog.quality_checklists.category = part_groups.category_label · 이 범주에서 무엇을 확인해야 하는지</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>확인 항목</t>
         </is>
       </c>
-      <c r="C22" s="41" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="C22" s="39" t="n"/>
+      <c r="D22" s="30" t="n"/>
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>이상 시 조치</t>
         </is>
       </c>
-      <c r="F22" s="41" t="n"/>
-      <c r="G22" s="41" t="n"/>
-      <c r="H22" s="32" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="39" t="n"/>
+      <c r="H22" s="30" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="42" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>입고 검사</t>
         </is>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>{{incoming_inspection}}</t>
         </is>
       </c>
-      <c r="E23" s="37" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>{{action_on_anomaly}}</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>조립·보관</t>
         </is>
       </c>
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>{{assembly_control}}</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>기능·신뢰성</t>
         </is>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>{{reliability_test}}</t>
         </is>
@@ -2045,7 +2037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2065,119 +2057,119 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>대체품 후보        [조회 시점 참조]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>불량유형이 CRACK일 때만 첨부된다 · MISSING · POSITION_ERROR · ORIENTATION_ERROR는 조립 불량이므로 대체품이 대책이 되지 않는다</t>
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>불량 유형과 무관하게 항상 첨부한다 · 부품 교체가 이번 건의 대책인지는 ② 발생 원인을 확정한 담당자가 판단한다</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>동일 정격만으로 drop-in 판단 금지 · 「필수 재검증」을 모두 통과하고 변경 승인이 완료된 뒤에만 적용한다.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>조회 시각 {{queried_at}}   ·   데이터시트 {{source_file}} (기준일 {{source_dated_on}})   ·   Group ID {{group_id}} ({{category_label}})   ·   후보 {{candidate_count}}종   ·   행은 후보 수만큼 반복</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>대체코드</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>제조사 / P/N</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>핵심 사양·용도</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>상호호환 상태</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>필수 재검증</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>{{defect_type}} 관련 소견</t>
         </is>
       </c>
-      <c r="H6" s="31" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>Source · 확인일</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>{{candidate_role}}</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>{{alternate_code}}</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>{{manufacturer}} / {{manufacturer_part_number}}</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>{{key_spec}}</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>{{compatibility_status}}</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>{{revalidation_items}}</t>
         </is>
       </c>
-      <c r="G7" s="37" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>{{defect_relevance}}</t>
         </is>
       </c>
-      <c r="H7" s="37" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>{{source_id}} · {{checked_at}}</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>단가·MOQ·재고·리드타임·공급사는 이 문서에 싣지 않는다. 조회 시점에 이미 상하는 값이고 품질 담당자의 결정 변수가 아니다 → GET /parts/{part_id} 또는 구매 담당</t>
         </is>

--- a/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
+++ b/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
@@ -276,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -401,6 +401,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -849,7 +852,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>{{part_id}} · {{part_name}} ({{group_id}} / {{category_label}})</t>
+          <t>{{part_id}} · {{part_name}} ({{category_label}})</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1496,7 +1499,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>defect_report.alert_evidence 스냅샷 · 문서번호 {{alert_code}} · 수정 금지</t>
+          <t>production.unit_defects 확정 기록 · 문서번호 {{alert_code}} · 수정 금지</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1939,7 @@
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>datastation_part_checklist · part_catalog.quality_checklists.category = part_groups.category_label · 이 범주에서 무엇을 확인해야 하는지</t>
+          <t>데이터시트 Checklist 시트 · 범주 = part_groups.category_label · 이 범주에서 무엇을 확인해야 하는지</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2046,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -2073,116 +2074,96 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="41" t="inlineStr">
         <is>
-          <t>동일 정격만으로 drop-in 판단 금지 · 「필수 재검증」을 모두 통과하고 변경 승인이 완료된 뒤에만 적용한다.</t>
+          <t>같은 부품 타입이라는 것 외에 검증된 것은 없다 · 동일 정격만으로 drop-in 판단 금지 · 핀/패키지/정격/열/수명 재검증과 변경 승인을 거친 뒤에만 적용한다.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
         <is>
-          <t>조회 시각 {{queried_at}}   ·   데이터시트 {{source_file}} (기준일 {{source_dated_on}})   ·   Group ID {{group_id}} ({{category_label}})   ·   후보 {{candidate_count}}종   ·   행은 후보 수만큼 반복</t>
+          <t>조회 시각 {{queried_at}}   ·   데이터시트 {{source_file}} (기준일 {{source_dated_on}})   ·   부품 타입 {{category_label}}   ·   후보 {{candidate_count}}종   ·   단가 {{price_range}}   ·   현재 선정 {{price_selected}}</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>제조사 / P/N</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>대체코드</t>
+          <t>핵심 정격</t>
         </is>
       </c>
       <c r="C6" s="29" t="inlineStr">
         <is>
-          <t>제조사 / P/N</t>
+          <t>공급사</t>
         </is>
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>핵심 사양·용도</t>
+          <t>단가</t>
         </is>
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>상호호환 상태</t>
+          <t>가격 기준 수량</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
         <is>
-          <t>필수 재검증</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t>{{defect_type}} 관련 소견</t>
-        </is>
-      </c>
-      <c r="H6" s="29" t="inlineStr">
-        <is>
-          <t>Source · 확인일</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
+          <t>가격 확인일</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>{{candidate_role}}</t>
+          <t>{{manufacturer_part_number}}</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>{{alternate_code}}</t>
+          <t>{{key_spec}}</t>
         </is>
       </c>
       <c r="C7" s="35" t="inlineStr">
         <is>
-          <t>{{manufacturer}} / {{manufacturer_part_number}}</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="inlineStr">
-        <is>
-          <t>{{key_spec}}</t>
+          <t>{{supplier}}</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>{{unit_price}}</t>
         </is>
       </c>
       <c r="E7" s="35" t="inlineStr">
         <is>
-          <t>{{compatibility_status}}</t>
+          <t>{{price_basis}}</t>
         </is>
       </c>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>{{revalidation_items}}</t>
-        </is>
-      </c>
-      <c r="G7" s="35" t="inlineStr">
-        <is>
-          <t>{{defect_relevance}}</t>
-        </is>
-      </c>
-      <c r="H7" s="35" t="inlineStr">
-        <is>
-          <t>{{source_id}} · {{checked_at}}</t>
+          <t>{{price_checked_at}}</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="inlineStr">
-        <is>
-          <t>단가·MOQ·재고·리드타임·공급사는 이 문서에 싣지 않는다. 조회 시점에 이미 상하는 값이고 품질 담당자의 결정 변수가 아니다 → GET /parts/{part_id} 또는 구매 담당</t>
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>단가는 데이터시트 기준일의 값이고 발주 근거가 아니다. MOQ·재고·리드타임과 상호호환 판정은 이 문서에 없다 → GET /parts/{part_id} 또는 구매·품질 담당</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
   <mergeCells count="5">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
+++ b/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
@@ -30,6 +30,8 @@
     <definedName name="reply_closure_note">'검증'!$B$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$H$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'검증'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'근거'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'판단자료'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -51,8 +53,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
       <color rgb="00262626"/>
-      <sz val="9"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -68,9 +71,8 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <b val="1"/>
       <color rgb="00262626"/>
-      <sz val="8"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -157,7 +159,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -202,6 +204,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCE3EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -279,7 +291,7 @@
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -287,19 +299,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -340,7 +352,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -350,15 +362,15 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -371,33 +383,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -482,6 +494,61 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="2857500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -787,7 +854,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>{{part_id}}</t>
+        </is>
+      </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
           <t>불  량  대  책  서</t>
@@ -888,7 +959,28 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="6" customHeight="1"/>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>발행 대상</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Job {{job_id}} · Unit {{target_unit_id}} · {{target_slot_code}}</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>검사 시각</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>{{target_inspected_at}}</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
@@ -1016,12 +1108,12 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>실제 PPM (기준 {{threshold_ppm}})</t>
+          <t>발행 시점 PPM</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>기준 대비</t>
+          <t>발행 기준</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -1060,7 +1152,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>발생 집중</t>
+          <t>발생 위치</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1070,12 +1162,12 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>직전 기간 대비</t>
+          <t>데이터시트 대조</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>{{trend_vs_prev}}</t>
+          <t>{{datasheet_match}}</t>
         </is>
       </c>
     </row>
@@ -1239,14 +1331,16 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="37">
+  <mergeCells count="39">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="B26:H27"/>
+    <mergeCell ref="B8:D8"/>
     <mergeCell ref="B1:D3"/>
+    <mergeCell ref="F8:H8"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="H2:H3"/>
@@ -1282,12 +1376,12 @@
     <dataValidation sqref="F6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK" promptTitle="불량 유형" prompt="별지 3장은 유형과 무관하게 항상 첨부한다.&#10;어느 자료가 이번 건에 쓸모 있는지는 담당자가 판단한다." type="list">
       <formula1>"MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK"</formula1>
     </dataValidation>
-    <dataValidation sqref="B21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 협조가 필요한 조치" prompt="담당자 혼자 결정할 수 없는 항목이다. 해당하는 것의 ☐ 를 ☑ 로 바꾸고,&#10;아래 칸에 누구에게 언제 요청했는지 적는다.&#10;&#10;생산 중단 → 생산팀장 · 출하 보류 → 영업/물류 · 재고 선별 → 인력 투입 승인&#10;고객 통보 → 품질보증 책임자 · 설비 정지 → 설비팀&#10;→ containment_summary 첫 줄로 함께 저장된다"/>
-    <dataValidation sqref="B22" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 초동 조치 — 오늘 안에" prompt="격리·선별·출하보류 범위와 완료 시각을 적는다.&#10;영향 받는 job_id / unit_id 범위를 함께 적는다.&#10;&#10;원인이 안 나와도 오늘 회신한다. 여기는 '막았는지'만 쓰는 칸이다.&#10;원인을 없애는 것은 ④ 이고, 이 칸은 확산을 멈추는 칸이다.&#10;→ alert_countermeasures.containment_summary"/>
-    <dataValidation sqref="B25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 한 줄 요약 (40자)" prompt="아래 본문을 한 줄로 줄인 것. 예: '배치 하강속도 상향 + 지지 핀 최원거리 슬롯'&#10;&#10;이 부품·유형이 다시 나면, 다음 대책서의 자동 분석 ③ 줄이 이 칸을 그대로 읽어&#10;'과거 원인'으로 싣는다. 본문은 길어서 그 자리에 들어가지 않는다.&#10;→ alert_countermeasures.root_cause_label"/>
-    <dataValidation sqref="B26" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 왜 만들어졌는가" prompt="「판단자료」 A·B로 급증 시점과 레시피 변경 시점을 대조한다.&#10;재현 또는 실물 확인으로 검증한 근거를 적는다.&#10;가설이면 '가설'이라고 표시한다.&#10;→ alert_countermeasures.root_cause_summary"/>
-    <dataValidation sqref="B28" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="③ 유출 원인 — 왜 검사에서 걸리지 않았는가" prompt="「판단자료」 D의 검사 항목과 대조해 판정 기준의 한계를 적는다.&#10;검사를 안 한 것인지, 했는데 못 걸른 것인지 구분한다.&#10;→ alert_countermeasures.escape_cause_summary"/>
-    <dataValidation sqref="B31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="④ 재발방지 대책 — 원인을 제거하는 영구대책" prompt="레시피·공정조건을 바꾸면 변경 후 recipe_version을 적는다.&#10;부품을 바꾸면 「대체품」 시트의 대체코드를 적는다.&#10;동일 부품을 쓰는 다른 슬롯으로의 수평전개 여부를 포함한다.&#10;&#10;레시피 변경은 변경관리 승인이, 부품 교체는 고객 승인이 필요할 수 있다.&#10;승인 절차가 걸리면 그 일정도 함께 적는다.&#10;→ alert_countermeasures.applied_recipe_version / applied_at"/>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 협조가 필요한 조치" prompt="담당자 혼자 결정할 수 없는 항목이다. 해당하는 것의 ☐ 를 ☑ 로 바꾸고,&#10;아래 칸에 누구에게 언제 요청했는지 적는다.&#10;&#10;생산 중단 → 생산팀장 · 출하 보류 → 영업/물류 · 재고 선별 → 인력 투입 승인&#10;고객 통보 → 품질보증 책임자 · 설비 정지 → 설비팀&#10;"/>
+    <dataValidation sqref="B22" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 초동 조치 — 오늘 안에" prompt="격리·선별·출하보류 범위와 완료 시각을 적는다.&#10;영향 받는 job_id / unit_id 범위를 함께 적는다.&#10;&#10;원인이 안 나와도 오늘 회신한다. 여기는 '막았는지'만 쓰는 칸이다.&#10;원인을 없애는 것은 ④ 이고, 이 칸은 확산을 멈추는 칸이다.&#10;"/>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 한 줄 요약 (40자)" prompt="아래 본문을 한 줄로 줄인 것. 예: '배치 하강속도 상향 + 지지 핀 최원거리 슬롯'&#10;본문은 길어서 이 칸에 들어가지 않으므로 핵심 원인만 적는다."/>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 왜 만들어졌는가" prompt="「근거」의 발생 기록과 검사 이미지를 확인한다.&#10;재현 또는 실물 확인으로 검증한 근거를 적는다.&#10;가설이면 '가설'이라고 표시한다.&#10;"/>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="③ 유출 원인 — 왜 검사에서 걸리지 않았는가" prompt="「판단자료」의 데이터시트 검사 항목과 대조해 판정 기준의 한계를 적는다.&#10;검사를 안 한 것인지, 했는데 못 걸른 것인지 구분한다.&#10;"/>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="④ 재발방지 대책 — 원인을 제거하는 영구대책" prompt="레시피·공정조건을 바꾸면 변경 후 recipe_version을 적는다.&#10;부품을 바꾸면 「대체품」 시트의 대체코드를 적는다.&#10;동일 부품을 쓰는 다른 슬롯으로의 수평전개 여부를 포함한다.&#10;&#10;레시피 변경은 변경관리 승인이, 부품 교체는 고객 승인이 필요할 수 있다.&#10;승인 절차가 걸리면 그 일정도 함께 적는다.&#10;"/>
   </dataValidations>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1456,17 +1550,17 @@
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <dataValidations count="9">
-    <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: PENDING,EFFECTIVE,INEFFECTIVE" promptTitle="⑤ 판정" prompt="기준 불량률 이하면 EFFECTIVE · 아니면 INEFFECTIVE로 두고 ②로 되돌아간다." type="list">
+    <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: PENDING,EFFECTIVE,INEFFECTIVE" promptTitle="⑤ 판정" prompt="품질 절차에서 정한 판정 기준에 따라 선택한다." type="list">
       <formula1>"PENDING,EFFECTIVE,INEFFECTIVE"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 기간" prompt="대책을 적용하고 다시 집계한 구간. [시작, 끝) 으로 적는다.&#10;검증 물량이 기준 최소 건수를 넘어야 판정할 수 있다."/>
-    <dataValidation sqref="D5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 적용 레시피" prompt="대책을 적용한 뒤 실행한 recipe_version.&#10;이 값이 있어야 적용 전후를 같은 제품 안에서 비교할 수 있다.&#10;→ alert_countermeasures.applied_recipe_version"/>
-    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 검사 수량" prompt="부품 기준 검사 건수 (유닛 수 × 해당 부품 슬롯 수).&#10;→ alert_countermeasures.verified_inspected_quantity"/>
-    <dataValidation sqref="F5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 불량 수량" prompt="→ alert_countermeasures.verified_defective_quantity"/>
-    <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정" prompt="기준 불량률 이하로 내려왔으면 EFFECTIVE.&#10;아니면 INEFFECTIVE로 두고 ②로 되돌아간다.&#10;→ alert_countermeasures.verification_status"/>
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정 근거" prompt="재집계 결과를 그렇게 읽은 이유.&#10;검증 수량이 기준 최소 건수에 못 미치면 그것도 적는다."/>
-    <dataValidation sqref="F8" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결일" prompt="→ alerts.closed_at · alert_status='CLOSED'"/>
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결 의견" prompt="잔여 위험과 종결 승인 의견.&#10;→ alert_countermeasures.closure_note / closed_by"/>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 기간" prompt="대책을 적용하고 다시 집계한 구간. [시작, 끝) 으로 적는다.&#10;"/>
+    <dataValidation sqref="D5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 적용 레시피" prompt="대책을 적용한 뒤 실행한 recipe_version.&#10;이 값이 있어야 적용 전후를 같은 제품 안에서 비교할 수 있다.&#10;"/>
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 검사 수량" prompt="부품 기준 검사 건수 (유닛 수 × 해당 부품 슬롯 수).&#10;"/>
+    <dataValidation sqref="F5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 불량 수량" prompt=""/>
+    <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정" prompt="판정 기준과 비교한 결론을 선택한다.&#10;기준은 해당 품질 절차에서 확인한다."/>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정 근거" prompt="재집계 결과를 그렇게 읽은 이유.&#10;"/>
+    <dataValidation sqref="F8" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결일" prompt=""/>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결 의견" prompt="잔여 위험과 종결 승인 의견.&#10;"/>
   </dataValidations>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1479,7 +1573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1616,18 +1710,44 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>검사 이미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>{{inspection_image_status}} · {{inspection_image_path}} · SHA-256 {{inspection_image_sha256}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="34" t="n"/>
+    </row>
+    <row r="14" ht="40" customHeight="1"/>
+    <row r="15" ht="40" customHeight="1"/>
+    <row r="16" ht="40" customHeight="1"/>
+    <row r="17" ht="40" customHeight="1"/>
+    <row r="18" ht="40" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
-  <mergeCells count="6">
+  <mergeCells count="9">
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A13:E18"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1637,406 +1757,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>판단 자료</t>
+          <t>품질 기준        [조회 시점 참조]</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>담당자가 ②발생 원인 · ③유출 원인을 좁히는 데 쓰는 참고 자료 · 자동 조회 · 결재 대상 아님</t>
+          <t>부품 데이터시트 Checklist 시트에서 조회 · 원인 자동 추정 자료가 아님</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
-        <is>
-          <t>판단 순서    ①「근거」어느 슬롯에 몰렸나  →  ② A 언제부터 올랐나  →  ③ B 그때 무엇이 바뀌었나  →  ④ C 전에도 있었나  →  ⑤ D 무엇을 확인하나</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>부품 범주 {{category_label}} · 데이터시트 대조 {{datasheet_match}} · 기준일 {{source_dated_on}} · 조회 {{queried_at}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="28" t="inlineStr">
         <is>
-          <t>A.  주차별 추세        [발행 시점 고정]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>언제부터 올라갔는지 · 급변 시점과 아래 B의 레시피 변경 시점을 대조한다. 주차 경계와 대책서 집계 구간은 일치하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>주차</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>검사 수량</t>
-        </is>
-      </c>
-      <c r="C7" s="29" t="inlineStr">
-        <is>
-          <t>불량 수량</t>
-        </is>
-      </c>
-      <c r="D7" s="29" t="inlineStr">
-        <is>
-          <t>불량률</t>
-        </is>
-      </c>
-      <c r="E7" s="29" t="inlineStr">
-        <is>
-          <t>기준 대비</t>
-        </is>
-      </c>
-      <c r="F7" s="29" t="inlineStr">
-        <is>
-          <t>레시피</t>
-        </is>
-      </c>
-      <c r="G7" s="29" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="H7" s="30" t="n"/>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>{{week}}</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>{{inspected}}</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>{{defective}}</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>{{rate}}</t>
-        </is>
-      </c>
-      <c r="E8" s="34" t="inlineStr">
-        <is>
-          <t>{{vs_threshold}}</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>{{recipe_version}}</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>{{note}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>B.  레시피 변경 전후 불량률        [발행 시점 고정]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="14" customHeight="1">
+          <t>데이터시트 품질 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>확인 항목</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>이상 시 조치</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>입고 검사</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>{{incoming_inspection}}</t>
+        </is>
+      </c>
+      <c r="E7" s="38" t="inlineStr">
+        <is>
+          <t>{{action_on_anomaly}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>조립·보관</t>
+        </is>
+      </c>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>{{assembly_control}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>기능·신뢰성</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>{{reliability_test}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>datastation_part_rates · 공정 조건이 원인인지 부품이 원인인지 가르는 1차 근거</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>레시피</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>적용 기간</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t>검사 수량</t>
-        </is>
-      </c>
-      <c r="D12" s="29" t="inlineStr">
-        <is>
-          <t>불량 수량</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="inlineStr">
-        <is>
-          <t>불량률</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>기준 대비</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
-        <is>
-          <t>변경 내용</t>
-        </is>
-      </c>
-      <c r="H12" s="30" t="n"/>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>{{recipe_version}}</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>{{applied_period}}</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>{{inspected}}</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>{{defective}}</t>
-        </is>
-      </c>
-      <c r="E13" s="26" t="inlineStr">
-        <is>
-          <t>{{rate}}</t>
-        </is>
-      </c>
-      <c r="F13" s="34" t="inlineStr">
-        <is>
-          <t>{{vs_threshold}}</t>
-        </is>
-      </c>
-      <c r="G13" s="35" t="inlineStr">
-        <is>
-          <t>{{change_note}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>C.  동일 부품 · 동일 유형 과거 대책서        [발행 시점 고정]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>datastation_alerts · 재발이면 이전 대책이 왜 듣지 않았는지부터 확인한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
-        <is>
-          <t>문서번호</t>
-        </is>
-      </c>
-      <c r="B17" s="29" t="inlineStr">
-        <is>
-          <t>집계 기간</t>
-        </is>
-      </c>
-      <c r="C17" s="29" t="inlineStr">
-        <is>
-          <t>불량률</t>
-        </is>
-      </c>
-      <c r="D17" s="29" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="E17" s="29" t="inlineStr">
-        <is>
-          <t>적용 대책</t>
-        </is>
-      </c>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="29" t="inlineStr">
-        <is>
-          <t>당시 근본 원인</t>
-        </is>
-      </c>
-      <c r="H17" s="30" t="n"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
-        <is>
-          <t>{{alert_code}}</t>
-        </is>
-      </c>
-      <c r="B18" s="36" t="inlineStr">
-        <is>
-          <t>{{period}}</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>{{defect_rate}}</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>{{alert_status}}</t>
-        </is>
-      </c>
-      <c r="E18" s="38" t="inlineStr">
-        <is>
-          <t>{{applied_recipe_version}} / {{applied_at}}</t>
-        </is>
-      </c>
-      <c r="G18" s="35" t="inlineStr">
-        <is>
-          <t>{{root_cause_summary}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>D.  품질 체크리스트        [조회 시점 참조 · 데이터시트 갱신 시 바뀜]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>데이터시트 Checklist 시트 · 범주 = part_groups.category_label · 이 범주에서 무엇을 확인해야 하는지</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B22" s="29" t="inlineStr">
-        <is>
-          <t>확인 항목</t>
-        </is>
-      </c>
-      <c r="C22" s="39" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="29" t="inlineStr">
-        <is>
-          <t>이상 시 조치</t>
-        </is>
-      </c>
-      <c r="F22" s="39" t="n"/>
-      <c r="G22" s="39" t="n"/>
-      <c r="H22" s="30" t="n"/>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="40" t="inlineStr">
-        <is>
-          <t>입고 검사</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>{{incoming_inspection}}</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>{{action_on_anomaly}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="40" t="inlineStr">
-        <is>
-          <t>조립·보관</t>
-        </is>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>{{assembly_control}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="40" t="inlineStr">
-        <is>
-          <t>기능·신뢰성</t>
-        </is>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>{{reliability_test}}</t>
+          <t>원본 {{source_file}}</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
-  <mergeCells count="25">
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="B23:D23"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E7:H9"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E23:H25"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2046,7 +1894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2060,99 +1908,163 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>대체품 후보        [조회 시점 참조]</t>
+          <t>현재 부품과 대체품 후보        [조회 시점 참조]</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>불량 유형과 무관하게 항상 첨부한다 · 부품 교체가 이번 건의 대책인지는 ② 발생 원인을 확정한 담당자가 판단한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+          <t>DB parts: {{part_id}} / {{part_name}} / {{category_label}} · 데이터시트 MPN 대조: {{datasheet_match}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>현재 MPN</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>핵심 정격</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>공급사</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>가격 기준 수량</t>
+        </is>
+      </c>
+      <c r="F3" s="29" t="inlineStr">
+        <is>
+          <t>가격 확인일</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="50" customHeight="1">
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_mpn}}</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_spec}}</t>
+        </is>
+      </c>
+      <c r="C4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_supplier}}</t>
+        </is>
+      </c>
+      <c r="D4" s="40" t="inlineStr">
+        <is>
+          <t>{{selected_unit_price}}</t>
+        </is>
+      </c>
+      <c r="E4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_price_basis}}</t>
+        </is>
+      </c>
+      <c r="F4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_price_checked_at}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>같은 부품 타입이라는 것 외에 검증된 것은 없다 · 동일 정격만으로 drop-in 판단 금지 · 핀/패키지/정격/열/수명 재검증과 변경 승인을 거친 뒤에만 적용한다.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>조회 시각 {{queried_at}}   ·   데이터시트 {{source_file}} (기준일 {{source_dated_on}})   ·   부품 타입 {{category_label}}   ·   후보 {{candidate_count}}종   ·   단가 {{price_range}}   ·   현재 선정 {{price_selected}}</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>제조사 / P/N</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>핵심 정격</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>공급사</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>단가</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>가격 기준 수량</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>가격 확인일</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>{{manufacturer_part_number}}</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>{{key_spec}}</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>{{supplier}}</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>{{unit_price}}</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>{{price_basis}}</t>
         </is>
       </c>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="F10" s="38" t="inlineStr">
         <is>
           <t>{{price_checked_at}}</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>단가는 데이터시트 기준일의 값이고 발주 근거가 아니다. MOQ·재고·리드타임과 상호호환 판정은 이 문서에 없다 → GET /parts/{part_id} 또는 구매·품질 담당</t>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>단가는 데이터시트 기준일의 값이고 발주 근거가 아니다. MOQ·재고·리드타임과 상호호환 판정은 이 문서에 없다 → GET /parts/{{part_id}} 또는 구매·품질 담당</t>
         </is>
       </c>
     </row>
@@ -2161,9 +2073,9 @@
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
+++ b/MAIN_SERVER/templates/불량대책서_표준양식.xlsx
@@ -43,7 +43,7 @@
     <numFmt numFmtId="164" formatCode="0.0&quot;배&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,7 +106,7 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00262626"/>
-      <sz val="8.5"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -123,11 +123,6 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00808080"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00262626"/>
       <sz val="8"/>
     </font>
     <font>
@@ -336,7 +331,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -348,7 +343,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -356,10 +351,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -373,36 +368,36 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -411,13 +406,13 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1149,7 +1144,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t>발생 위치</t>
@@ -1162,12 +1157,13 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>데이터시트 대조</t>
+          <t>제조사 P/N</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>{{datasheet_match}}</t>
+          <t>{{datasheet_match}} · {{selected_mpn}}
+정격 {{selected_spec}} · 공급사 {{selected_supplier}}</t>
         </is>
       </c>
     </row>
